--- a/Agile project tracking/Unit_Test_Plan_v0.1.xlsx
+++ b/Agile project tracking/Unit_Test_Plan_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumba\Desktop\tracker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumba\Desktop\CRSA-Agent\Agile project tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3FBEFA-C1A3-4AC4-AD68-C0FA767A68F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1436EE-D271-45A3-9E0B-DF2AF3BAC86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Actual Result</t>
   </si>
@@ -88,24 +88,59 @@
   </si>
   <si>
     <t>system must detect error</t>
+  </si>
+  <si>
+    <t>Code Analysis in Java</t>
+  </si>
+  <si>
+    <t>Provide a valid Java code file to the Code Analysis Agent.</t>
+  </si>
+  <si>
+    <t>Detect code smells and poor coding practices in Java code.</t>
+  </si>
+  <si>
+    <t>Display code-quality findings with descriptions, severity, and recommendations.</t>
+  </si>
+  <si>
+    <t>Code Analysis in Python</t>
+  </si>
+  <si>
+    <t>Provide a valid Python code file to the Code Analysis Agent.</t>
+  </si>
+  <si>
+    <t>Detect code smells and complexity issues in Python code.</t>
+  </si>
+  <si>
+    <t>Security Analysis in Java</t>
+  </si>
+  <si>
+    <t>Provide a valid Java code file containing a potential security vulnerability.</t>
+  </si>
+  <si>
+    <t>Detect security vulnerabilities in Java code.</t>
+  </si>
+  <si>
+    <t>Display identified vulnerabilities with severity, descriptions, and remediation suggestions.</t>
+  </si>
+  <si>
+    <t>Security Analysis in Python</t>
+  </si>
+  <si>
+    <t>Provide a valid Python code file containing a potential security vulnerability.</t>
+  </si>
+  <si>
+    <t>Detect security vulnerabilities in Python code.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -157,16 +192,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -485,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -519,19 +548,19 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -539,19 +568,19 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -559,45 +588,109 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+    <row r="5" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
